--- a/files/survey_results.xlsx
+++ b/files/survey_results.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,6 +915,29 @@
         </is>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>8326151060</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Ali</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Soliyev</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>1</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>Ha</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
